--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039306</v>
+        <v>0.038436</v>
       </c>
       <c r="C3" t="n">
-        <v>0.47619</v>
+        <v>0.465646</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03868</v>
+        <v>0.037927</v>
       </c>
       <c r="C4" t="n">
-        <v>0.984053</v>
+        <v>0.98676</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.038436</v>
+        <v>0.038533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.465646</v>
+        <v>0.466826</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.037927</v>
+        <v>0.038039</v>
       </c>
       <c r="C4" t="n">
-        <v>0.98676</v>
+        <v>0.987172</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.038533</v>
+        <v>0.040586</v>
       </c>
       <c r="C3" t="n">
-        <v>0.466826</v>
+        <v>0.491693</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.038039</v>
+        <v>0.039927</v>
       </c>
       <c r="C4" t="n">
-        <v>0.987172</v>
+        <v>0.983753</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.040586</v>
+        <v>0.040352</v>
       </c>
       <c r="C3" t="n">
-        <v>0.491693</v>
+        <v>0.488861</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039927</v>
+        <v>0.039653</v>
       </c>
       <c r="C4" t="n">
-        <v>0.983753</v>
+        <v>0.982683</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.040352</v>
+        <v>0.038525</v>
       </c>
       <c r="C3" t="n">
-        <v>0.488861</v>
+        <v>0.466723</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039653</v>
+        <v>0.03782</v>
       </c>
       <c r="C4" t="n">
-        <v>0.982683</v>
+        <v>0.981708</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.038525</v>
+        <v>0.040408</v>
       </c>
       <c r="C3" t="n">
-        <v>0.466723</v>
+        <v>0.489541</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03782</v>
+        <v>0.039326</v>
       </c>
       <c r="C4" t="n">
-        <v>0.981708</v>
+        <v>0.973221</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.040408</v>
+        <v>0.040577</v>
       </c>
       <c r="C3" t="n">
-        <v>0.489541</v>
+        <v>0.49158</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039326</v>
+        <v>0.039523</v>
       </c>
       <c r="C4" t="n">
-        <v>0.973221</v>
+        <v>0.974029</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.040577</v>
+        <v>0.038265</v>
       </c>
       <c r="C3" t="n">
-        <v>0.49158</v>
+        <v>0.463569</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039523</v>
+        <v>0.038265</v>
       </c>
       <c r="C4" t="n">
-        <v>0.974029</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.038265</v>
+        <v>0.03797</v>
       </c>
       <c r="C3" t="n">
-        <v>0.463569</v>
+        <v>0.460005</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.038265</v>
+        <v>0.03797</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03797</v>
+        <v>0.039205</v>
       </c>
       <c r="C3" t="n">
-        <v>0.460005</v>
+        <v>0.474963</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03797</v>
+        <v>0.039205</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039205</v>
+        <v>0.039551</v>
       </c>
       <c r="C3" t="n">
-        <v>0.474963</v>
+        <v>0.479158</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039205</v>
+        <v>0.039551</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039551</v>
+        <v>0.039727</v>
       </c>
       <c r="C3" t="n">
-        <v>0.479158</v>
+        <v>0.481285</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039551</v>
+        <v>0.039727</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08254300000000001</v>
+        <v>0.05382</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.039727</v>
+        <v>0.07292999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.481285</v>
+        <v>1.355074</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.039727</v>
+        <v>0.07292999999999999</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07292999999999999</v>
+        <v>0.073058</v>
       </c>
       <c r="C3" t="n">
-        <v>1.355074</v>
+        <v>1.35744</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07292999999999999</v>
+        <v>0.073058</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.073058</v>
+        <v>0.07230399999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1.35744</v>
+        <v>1.343437</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.073058</v>
+        <v>0.07230399999999999</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07230399999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="C3" t="n">
-        <v>1.343437</v>
+        <v>1.343372</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07230399999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>

--- a/vignettes/vignette-1/worked_example_size_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_size_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0723</v>
+        <v>0.072947</v>
       </c>
       <c r="C3" t="n">
-        <v>1.343372</v>
+        <v>1.355378</v>
       </c>
     </row>
     <row r="4">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0723</v>
+        <v>0.072947</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
